--- a/Assets/Data/Rules.xlsx
+++ b/Assets/Data/Rules.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -29,23 +29,18 @@
     <t>Open</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Text</t>
   </si>
   <si>
     <t>Help</t>
   </si>
   <si>
-    <t>ゲーム内容</t>
-  </si>
-  <si>
-    <t>「Norm」はステージ・バトル2パートにわけられます。
-ステージはマスを選択して進んでいきます。
-選択したマスに応じて様々なイベントが発生します。
-バトルマスを選択した場合は敵とバトルを行います。
-勝利すると次のマスが選択できるようになります。</t>
+    <t>ゲームの目的</t>
+  </si>
+  <si>
+    <t>Normは全6層からなるステージをクリアすることが目的です。
+マスを選択してステージを進め、
+各階層にいるボスを討伐することで次の階層に進めます。</t>
   </si>
   <si>
     <t>ステージ</t>
@@ -57,71 +52,56 @@
 </t>
   </si>
   <si>
-    <t>探索コマンド</t>
-  </si>
-  <si>
-    <t>探索コマンドでマスを選択します。
-■魔物討伐
-マスに陣取る敵とバトルを行います。
-勝利すると次のマスに進めます。
-敗北した場合はバトル前の状態に戻りペナルティはありません。
+    <t>マスの種類</t>
+  </si>
+  <si>
+    <t>■魔物殲滅
+メンバーを選んで敵とバトルを行います。
+勝利するとバトルに参加したメンバーのLvが1上がります。
+敗北した場合でもペナルティはなくバトル前の状態に戻ります。
 ■使途殲滅
-特別な敵とのバトルを行います。
+各階層のボスとバトルを行います。
+基本的に魔物殲滅と変わりません。
+■魔法選択
+候補の中から魔法を1つだけ選択して入手できます。
+入手した魔法は(Nu)を消費してメンバーに習得させることができます。
+■ショップ
+候補の中から魔法を(Nu)を消費して入手できます。
+(Nu)を消費しますが選択できる魔法の数に限りはありません。
+■仲間加入
+候補の中から仲間を1名だけ選択して加入できます。
+■仲間召喚
+未加入の仲間を1名だけ選択して加入できます。
 ■トレジャー
-マスに設置されたリソースを入手します。
-■魔法入手
-マスに設置された魔法を入手します。
-■アシスト
-マスに設置された仲間を加入します。
-■仲間召喚
-未加入の仲間を選択して加入します。</t>
-  </si>
-  <si>
-    <t>Lvアップコマンド</t>
-  </si>
-  <si>
-    <t>リソースを消費してキャラクターのLvをあげます。
-Lvアップに必要なリソースはキャラクターのLvに応じて増加します。</t>
-  </si>
-  <si>
-    <t>魔法習得コマンド</t>
-  </si>
-  <si>
-    <t>リソースを消費してキャラクターに魔法を覚えさせます。
-魔法習得に必要なリソースは
-キャラクターの属性適正に応じて増減します。</t>
-  </si>
-  <si>
-    <t>キャラコマンド</t>
-  </si>
-  <si>
-    <t>キャラクターのステータスや習得魔法を確認できます。</t>
+(Nu)を獲得します。</t>
   </si>
   <si>
     <t>バトル</t>
   </si>
   <si>
-    <t>バトルは敵のHpを0にすると勝利します。
-キャラクター全てのHpが0になった場合は敗北となります。</t>
-  </si>
-  <si>
-    <t>バトル操作</t>
-  </si>
-  <si>
-    <t>バトルは作戦に基づいてキャラクターが行動するフルオートモードと
-プレイヤーが魔法と対象を選択するマニュアルモードがあります。
-フルオートとマニュアルはバトル中に切り替えられます。</t>
-  </si>
-  <si>
-    <t>作戦について</t>
-  </si>
-  <si>
-    <t>フルオートモードでは各キャラクターは
-作戦に基づいて自動で行動します。
-作戦はバトル前に編集することができます。
-作戦では使用魔法・使用対象といった条件を指定できます。
-キャラクターは優先順位の高い方から条件に一致した魔法を使用します。
-作戦に設定していない魔法は発動しません。</t>
+    <t>バトルは全てオートで進行します。
+バトルは味方か敵全員のHpが0になるか
+150ターンを超えるまで自動で進みます。</t>
+  </si>
+  <si>
+    <t>リザルト</t>
+  </si>
+  <si>
+    <t>バトルに勝利すると参加メンバーのLvがアップします。
+■勝利時
+バトルの内容に応じてバトル評価を入手します。
+バトル評価に応じて(Nu)獲得量がアップします。
+■敗北時
+敗北した場合でもペナルティはありません。
+同じ編成で再戦するか、別のマスを選び直して先に進むこともできます。</t>
+  </si>
+  <si>
+    <t>バトル評価</t>
+  </si>
+  <si>
+    <t>バトルで勝利するとバトル評価値を入手します。
+バトル評価の累積値に応じて
+バトルで勝利時に獲得する(Nu)にボーナス補正が入ります。</t>
   </si>
   <si>
     <t>行動順</t>
@@ -157,6 +137,83 @@
 キャラクターの会心率は0%です。
 会心率は魔法の効果で上げた会心率と
 命中率と回避率の差が100を超えた分の合計で計算されます。</t>
+  </si>
+  <si>
+    <t>ステータス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■Lv
+Lvはバトル勝利時、または(Nu)を使用してアップします。
+Lvに応じて魔法を習得することができます。
+■パラメータ
+HP：0になると戦闘不能になります。
+ATK：攻撃時のダメージ量に影響します。
+DEF：攻撃を受ける際のダメージ量に影響します。
+SPD：バトルの行動順に影響します。
+■属性適正値
+キャラ毎に5つの属性適正値があります。
+属性適正値は魔法習得する際の(Nu)使用量に影響します。
+■習得コスト
+属性適正値に応じて魔法習得する際の(Nu)使用量が変化します。
+また魔法のRankがRの場合は(Nu)使用量が2倍になります。
+</t>
+  </si>
+  <si>
+    <t>魔法種別</t>
+  </si>
+  <si>
+    <t>■魔法種別
+魔法にはそれぞれ種別があります。
+・Active
+バトルでターンがまわってきた際に使用します。
+基本的に同じターン内で発動する魔法の起点になります。
+・Passive
+(条件)を満たしたとき自動で発動します。
+Unique
+Passiveと同じく(条件)を満たしたとき自動で発動しさらに覚醒状態になります。
+バトル中1回だけ発動します。
+・Awaken
+Activeと同じくバトルでターンがまわってきた際に使用します。
+覚醒状態の場合にのみバトル中1回だけ発動できます。
+・Enhance
+習得している魔法の効果を強化します。
+効果は作戦に設定しなくても自動で発動します。
+・Relic
+編成しているキャラクター全体に自動で効果が発動します。</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>■Range
+魔法にはそれぞれ攻撃範囲があります。
+Range.Sの魔法はBackに配置した敵を対象にできません。
+ただしFrontに配置した敵がいない場合は使用できます。
+Range.Lの魔法は配置にかかわらず対象にできます。</t>
+  </si>
+  <si>
+    <t>CT（カウントターン）</t>
+  </si>
+  <si>
+    <t>■CT
+一部の魔法にはCT(カウントターン)があります。
+CTは魔法を使用した後、再度使用できるまでの猶予ターンです。</t>
+  </si>
+  <si>
+    <t>レベルアップ</t>
+  </si>
+  <si>
+    <t>■Lvアップ
+(Nu)を消費してメンバーのLvを上げることができます。
+消費量はLvが上がるにつれて増加します。</t>
+  </si>
+  <si>
+    <t>魔法習得</t>
+  </si>
+  <si>
+    <t>■魔法習得
+(Nu)を消費してメンバーに魔法を習得させることができます。
+消費量はメンバーの属性適正値によって増減します。</t>
   </si>
 </sst>
 </file>
@@ -164,9 +221,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -185,6 +242,88 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -193,66 +332,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -261,69 +340,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,187 +395,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,11 +589,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -556,6 +619,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -571,17 +643,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,19 +655,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,9 +678,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,145 +694,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1108,7 +1165,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1169,13 +1226,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>1130</v>
+        <v>2000</v>
       </c>
       <c r="B5">
-        <v>1130</v>
+        <v>2000</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1183,13 +1240,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>1140</v>
+        <v>2110</v>
       </c>
       <c r="B6">
-        <v>1140</v>
+        <v>2110</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1197,13 +1254,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>1150</v>
+        <v>2120</v>
       </c>
       <c r="B7">
-        <v>1150</v>
+        <v>2120</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1211,10 +1268,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2000</v>
+        <v>2130</v>
       </c>
       <c r="B8">
-        <v>2000</v>
+        <v>2130</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1225,10 +1282,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>2110</v>
+        <v>2140</v>
       </c>
       <c r="B9">
-        <v>2110</v>
+        <v>2140</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1239,10 +1296,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2120</v>
+        <v>2150</v>
       </c>
       <c r="B10">
-        <v>2120</v>
+        <v>2150</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1253,10 +1310,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="B11">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1267,13 +1324,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2140</v>
+        <v>3000</v>
       </c>
       <c r="B12">
-        <v>2140</v>
+        <v>3000</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1281,13 +1338,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2150</v>
+        <v>3010</v>
       </c>
       <c r="B13">
-        <v>2150</v>
+        <v>3010</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1295,21 +1352,72 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2160</v>
+        <v>3020</v>
       </c>
       <c r="B14">
-        <v>2160</v>
+        <v>3020</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>4</v>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>3030</v>
+      </c>
+      <c r="B15">
+        <v>3030</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>3040</v>
+      </c>
+      <c r="B16">
+        <v>3040</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>3050</v>
+      </c>
+      <c r="B17">
+        <v>3050</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>3050</v>
+      </c>
+      <c r="B18">
+        <v>3050</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1321,7 +1429,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="51.3636363636364" customWidth="1"/>
@@ -1333,21 +1441,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="78" spans="1:3">
+    </row>
+    <row r="2" ht="65" spans="1:3">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" ht="65" spans="1:3">
@@ -1355,141 +1463,165 @@
         <v>1110</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="286" spans="1:3">
+    </row>
+    <row r="4" ht="403" spans="1:3">
       <c r="A4">
         <v>1120</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:3">
       <c r="A5">
-        <v>1130</v>
-      </c>
-      <c r="B5" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" ht="143" spans="1:3">
+      <c r="A6">
+        <v>2110</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" ht="52" spans="1:3">
-      <c r="A6">
-        <v>1140</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" ht="52" spans="1:3">
+      <c r="A7">
+        <v>2120</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" ht="26" spans="1:3">
-      <c r="A7">
-        <v>1150</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" ht="91" spans="1:3">
+      <c r="A8">
+        <v>2130</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" ht="39" spans="1:3">
-      <c r="A8">
-        <v>2000</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" ht="78" spans="1:3">
+      <c r="A9">
+        <v>2140</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" ht="91" spans="1:3">
-      <c r="A9">
-        <v>2110</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="10" ht="26" spans="1:3">
+      <c r="A10">
+        <v>2150</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" ht="130" spans="1:3">
-      <c r="A10">
-        <v>2120</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="11" ht="104" spans="1:3">
+      <c r="A11">
+        <v>2160</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" ht="91" spans="1:3">
-      <c r="A11">
-        <v>2130</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="12" ht="286" spans="1:3">
+      <c r="A12">
+        <v>3000</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" ht="78" spans="1:3">
-      <c r="A12">
-        <v>2140</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="13" ht="364" spans="1:3">
+      <c r="A13">
+        <v>3010</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" ht="26" spans="1:3">
-      <c r="A13">
-        <v>2150</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" ht="104" spans="1:3">
       <c r="A14">
-        <v>2160</v>
+        <v>3020</v>
       </c>
       <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="15" ht="52" spans="1:3">
+      <c r="A15">
+        <v>3030</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="3:3">
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="3:3">
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="52" spans="1:3">
+      <c r="A16">
+        <v>3040</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="65" spans="1:3">
+      <c r="A17">
+        <v>3050</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="1"/>
@@ -1514,18 +1646,6 @@
     <row r="23" spans="2:3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
